--- a/Excel/racks_import.xlsx
+++ b/Excel/racks_import.xlsx
@@ -16,7 +16,7 @@
     <t>description</t>
   </si>
   <si>
-    <t>godown_id (replace with actual UUID)</t>
+    <t>godown_name</t>
   </si>
   <si>
     <t>Rack-1</t>
@@ -25,7 +25,7 @@
     <t>Rack-1 storage rack</t>
   </si>
   <si>
-    <t>REPLACE_WITH_GODOWN_UUID</t>
+    <t>Main Warehouse</t>
   </si>
   <si>
     <t>Rack-2</t>
